--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/06_Müşteri ve Sözleşme Yönetimi/EKG-SAT-FRM-01_satis_teklif_ve_siparis_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/06_Müşteri ve Sözleşme Yönetimi/EKG-SAT-FRM-01_satis_teklif_ve_siparis_formu.xlsx
@@ -983,7 +983,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-SAT-FRM-01&amp;C&amp;"Arial,Regular"&amp;11Satış Teklif ve Sipariş Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Teklifin teknik revizyon, vergi ve para birimi alanları ile eksik girdi hesapları düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>